--- a/CSDL_WebGIS_TruongTHPT_7TieuChi.xlsx
+++ b/CSDL_WebGIS_TruongTHPT_7TieuChi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\webgis_thpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588CF2CD-BFEE-45F2-A65C-AD07BB56520A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D044F1FC-1C1D-4579-95A0-AF6F2580183A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,15 +1036,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1380,7 +1380,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
@@ -1534,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="N3" s="5">
-        <v>1767000</v>
+        <v>2500000</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>32</v>
@@ -1627,7 +1627,7 @@
         <v>31</v>
       </c>
       <c r="N4" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>32</v>
@@ -1720,7 +1720,7 @@
         <v>31</v>
       </c>
       <c r="N5" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>32</v>
@@ -1813,7 +1813,7 @@
         <v>31</v>
       </c>
       <c r="N6" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>44</v>
@@ -1906,7 +1906,7 @@
         <v>31</v>
       </c>
       <c r="N7" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>49</v>
@@ -1991,7 +1991,7 @@
         <v>31</v>
       </c>
       <c r="N8" s="5">
-        <v>200000</v>
+        <v>6000000</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>55</v>
@@ -2076,7 +2076,7 @@
         <v>31</v>
       </c>
       <c r="N9" s="5">
-        <v>4000000</v>
+        <v>4600000</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>55</v>
@@ -2169,7 +2169,7 @@
         <v>31</v>
       </c>
       <c r="N10" s="5">
-        <v>200000</v>
+        <v>1200000</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>64</v>
@@ -2262,7 +2262,7 @@
         <v>31</v>
       </c>
       <c r="N11" s="5">
-        <v>200000</v>
+        <v>1200000</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>69</v>
@@ -2355,7 +2355,7 @@
         <v>31</v>
       </c>
       <c r="N12" s="5">
-        <v>2000000</v>
+        <v>2600000</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>74</v>
@@ -2448,7 +2448,7 @@
         <v>31</v>
       </c>
       <c r="N13" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>79</v>
@@ -2541,7 +2541,7 @@
         <v>31</v>
       </c>
       <c r="N14" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>83</v>
@@ -2634,7 +2634,7 @@
         <v>31</v>
       </c>
       <c r="N15" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>88</v>
@@ -2727,7 +2727,7 @@
         <v>31</v>
       </c>
       <c r="N16" s="5">
-        <v>1700000</v>
+        <v>2700000</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>92</v>
@@ -2812,7 +2812,7 @@
         <v>31</v>
       </c>
       <c r="N17" s="5">
-        <v>3200000</v>
+        <v>5200000</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>55</v>
@@ -2905,7 +2905,7 @@
         <v>31</v>
       </c>
       <c r="N18" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O18" s="4" t="s">
         <v>55</v>
@@ -2998,7 +2998,7 @@
         <v>31</v>
       </c>
       <c r="N19" s="5">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>103</v>
@@ -3091,7 +3091,7 @@
         <v>31</v>
       </c>
       <c r="N20" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O20" s="4" t="s">
         <v>107</v>
@@ -3184,7 +3184,7 @@
         <v>31</v>
       </c>
       <c r="N21" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>112</v>
@@ -3277,7 +3277,7 @@
         <v>31</v>
       </c>
       <c r="N22" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>116</v>
@@ -3370,7 +3370,7 @@
         <v>31</v>
       </c>
       <c r="N23" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>120</v>
@@ -3463,7 +3463,7 @@
         <v>31</v>
       </c>
       <c r="N24" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>124</v>
@@ -3556,7 +3556,7 @@
         <v>31</v>
       </c>
       <c r="N25" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>128</v>
@@ -3649,7 +3649,7 @@
         <v>31</v>
       </c>
       <c r="N26" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>133</v>
@@ -3742,7 +3742,7 @@
         <v>31</v>
       </c>
       <c r="N27" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>137</v>
@@ -3835,7 +3835,7 @@
         <v>31</v>
       </c>
       <c r="N28" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>141</v>
@@ -3920,7 +3920,7 @@
         <v>31</v>
       </c>
       <c r="N29" s="5">
-        <v>3600000</v>
+        <v>5600000</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>55</v>
@@ -4013,7 +4013,7 @@
         <v>31</v>
       </c>
       <c r="N30" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>149</v>
@@ -4106,7 +4106,7 @@
         <v>31</v>
       </c>
       <c r="N31" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>153</v>
@@ -4199,7 +4199,7 @@
         <v>31</v>
       </c>
       <c r="N32" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>158</v>
@@ -4292,7 +4292,7 @@
         <v>31</v>
       </c>
       <c r="N33" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O33" s="4" t="s">
         <v>162</v>
@@ -4385,7 +4385,7 @@
         <v>31</v>
       </c>
       <c r="N34" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>166</v>
@@ -4478,7 +4478,7 @@
         <v>31</v>
       </c>
       <c r="N35" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O35" s="4" t="s">
         <v>171</v>
@@ -4571,7 +4571,7 @@
         <v>31</v>
       </c>
       <c r="N36" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O36" s="4" t="s">
         <v>175</v>
@@ -4664,7 +4664,7 @@
         <v>31</v>
       </c>
       <c r="N37" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O37" s="4" t="s">
         <v>179</v>
@@ -4757,7 +4757,7 @@
         <v>31</v>
       </c>
       <c r="N38" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>184</v>
@@ -4850,7 +4850,7 @@
         <v>31</v>
       </c>
       <c r="N39" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O39" s="4" t="s">
         <v>189</v>
@@ -4943,7 +4943,7 @@
         <v>31</v>
       </c>
       <c r="N40" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>141</v>
@@ -5036,7 +5036,7 @@
         <v>31</v>
       </c>
       <c r="N41" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O41" s="4" t="s">
         <v>196</v>
@@ -5129,7 +5129,7 @@
         <v>31</v>
       </c>
       <c r="N42" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>200</v>
@@ -5222,7 +5222,7 @@
         <v>31</v>
       </c>
       <c r="N43" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O43" s="4" t="s">
         <v>204</v>
@@ -5315,7 +5315,7 @@
         <v>31</v>
       </c>
       <c r="N44" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>208</v>
@@ -5408,7 +5408,7 @@
         <v>31</v>
       </c>
       <c r="N45" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>212</v>
@@ -5501,7 +5501,7 @@
         <v>31</v>
       </c>
       <c r="N46" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>216</v>
@@ -5594,7 +5594,7 @@
         <v>31</v>
       </c>
       <c r="N47" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O47" s="4" t="s">
         <v>221</v>
@@ -5687,7 +5687,7 @@
         <v>31</v>
       </c>
       <c r="N48" s="5">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O48" s="4" t="s">
         <v>225</v>
@@ -5759,7 +5759,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>227</v>
       </c>
       <c r="B1" s="21"/>
@@ -5768,7 +5768,7 @@
       <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B2" s="21"/>
@@ -5843,7 +5843,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B10" s="21"/>
@@ -5932,7 +5932,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>252</v>
       </c>
       <c r="B16" s="21"/>
@@ -6077,7 +6077,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>271</v>
       </c>
       <c r="B25" s="21"/>
